--- a/testes/fixtures/planservi_amostra_1.xlsx
+++ b/testes/fixtures/planservi_amostra_1.xlsx
@@ -151,6 +151,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,6 +186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -219,20 +221,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -354,7 +352,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -9104,41 +9141,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="J5:T5"/>
-    <mergeCell ref="V5:AF5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="AS6:AT6"/>
-    <mergeCell ref="AS5:BB5"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="AU6:AV6"/>
-    <mergeCell ref="AW6:AX6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="AH5:AQ5"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="BA6:BB6"/>
-    <mergeCell ref="AP6:AQ6"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AE6:AE7"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="AY6:AZ6"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="M2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:BB68"/>
   </ignoredErrors>
@@ -9147,25 +9149,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:B3"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Rodovia:</v>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rodovia:</v>
-      </c>
-      <c r="B2" t="e">
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
         <v>Trecho:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A2:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>